--- a/fondos.xlsx
+++ b/fondos.xlsx
@@ -4688,13 +4688,13 @@
         <v>28</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>23</v>
@@ -4703,7 +4703,7 @@
         <v>40</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>42</v>
@@ -5270,16 +5270,16 @@
         <v>28</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>40</v>
@@ -9389,22 +9389,22 @@
         <v>28</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>40</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>42</v>
@@ -11004,13 +11004,13 @@
         <v>28</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G103" s="11" t="s">
         <v>23</v>
@@ -11019,7 +11019,7 @@
         <v>40</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>57</v>

--- a/fondos.xlsx
+++ b/fondos.xlsx
@@ -353,10 +353,10 @@
     <t xml:space="preserve">FdF Cred. Tendencias Globales CREDICORP SAF</t>
   </si>
   <si>
-    <t xml:space="preserve">CREDICORP ACCIONES EUROPA CREDICORP SAF</t>
+    <t xml:space="preserve">Desarrollados</t>
   </si>
   <si>
-    <t xml:space="preserve">Desarrollados</t>
+    <t xml:space="preserve">CREDICORP ACCIONES EUROPA CREDICORP SAF</t>
   </si>
   <si>
     <t xml:space="preserve">FdeF CRED ACC SECTOR SEGURID CREDICORP SAF</t>
@@ -5076,16 +5076,16 @@
         <v>28</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>40</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>93</v>
@@ -5182,7 +5182,7 @@
         <v>39</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>40</v>
@@ -5941,13 +5941,13 @@
         <v>28</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>29</v>
@@ -7771,10 +7771,10 @@
         <v>44</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>23</v>
@@ -7868,10 +7868,10 @@
         <v>44</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>23</v>
@@ -7962,16 +7962,16 @@
         <v>28</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>40</v>
@@ -8062,10 +8062,10 @@
         <v>44</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>23</v>
@@ -10818,13 +10818,13 @@
         <v>28</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>55</v>
@@ -13081,7 +13081,7 @@
         <v>39</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H125" s="11" t="s">
         <v>40</v>

--- a/fondos.xlsx
+++ b/fondos.xlsx
@@ -1162,7 +1162,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AL966"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.11"/>
@@ -4033,10 +4033,10 @@
         <v>27</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>21</v>
@@ -7529,13 +7529,13 @@
         <v>18</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>28</v>
@@ -10357,16 +10357,16 @@
         <v>27</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>37</v>
@@ -10467,16 +10467,16 @@
         <v>27</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>46</v>
@@ -11329,13 +11329,13 @@
         <v>27</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G94" s="11" t="s">
         <v>28</v>
@@ -11879,13 +11879,13 @@
         <v>18</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G99" s="11" t="s">
         <v>28</v>
@@ -12099,13 +12099,13 @@
         <v>27</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>22</v>
@@ -12209,13 +12209,13 @@
         <v>18</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G102" s="11" t="s">
         <v>22</v>
@@ -12427,13 +12427,13 @@
         <v>27</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G104" s="11" t="s">
         <v>22</v>
